--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21A.xlsx
@@ -129,25 +129,25 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>FFBA073E7C4A8BD35483A828B1751F77</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>543755216</t>
-  </si>
-  <si>
-    <t>4655021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/1er_Trimestre/Publicacion%20de%20Presupuesto%20COBAT-2022/Presupuesto%20De%20Ingresos%20y%20Egresos%202022%20COBAT.pdf</t>
+    <t>E31C3A4C4B9D07385D215AD9A59318FC</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>564688046</t>
+  </si>
+  <si>
+    <t>6391609</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/1er%20Trimestre/Publicacion%20de%20Presupuesto/PRESUPUESTO%202023.pdf</t>
   </si>
   <si>
     <t>https://www.transparenciapresupuestaria.gob.mx/</t>
@@ -156,7 +156,7 @@
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
-    <t>25/04/2022</t>
+    <t>25/04/2023</t>
   </si>
   <si>
     <t/>
@@ -183,7 +183,7 @@
     <t>Presupuesto por capítulo de gasto</t>
   </si>
   <si>
-    <t>235894F216DC39E23261339A8584E394</t>
+    <t>E9A4CE1D7739C4DD7F9794707D0C8C55</t>
   </si>
   <si>
     <t>1000</t>
@@ -192,10 +192,10 @@
     <t>Servicios personales</t>
   </si>
   <si>
-    <t>482935413</t>
-  </si>
-  <si>
-    <t>235894F216DC39E25B1E71F5263E65A8</t>
+    <t>501206101</t>
+  </si>
+  <si>
+    <t>E9A4CE1D7739C4DDC1E0F970A9BFEF07</t>
   </si>
   <si>
     <t>2000</t>
@@ -204,10 +204,10 @@
     <t>Materiales y suministros</t>
   </si>
   <si>
-    <t>8968534</t>
-  </si>
-  <si>
-    <t>235894F216DC39E29F29CAEA43FB648E</t>
+    <t>9112031</t>
+  </si>
+  <si>
+    <t>E9A4CE1D7739C4DD142FF48D758F21AD</t>
   </si>
   <si>
     <t>3000</t>
@@ -216,10 +216,10 @@
     <t>Servicios generales</t>
   </si>
   <si>
-    <t>44664539</t>
-  </si>
-  <si>
-    <t>235894F216DC39E28A7E5E5B1A2871B9</t>
+    <t>44875950</t>
+  </si>
+  <si>
+    <t>E9A4CE1D7739C4DD0547B141488060FC</t>
   </si>
   <si>
     <t>4000</t>
@@ -231,7 +231,7 @@
     <t>1400000</t>
   </si>
   <si>
-    <t>9ECC9B23D0F2FA702E4C8FDD18BD5708</t>
+    <t>E9A4CE1D7739C4DD07DE23DF4AF2B64C</t>
   </si>
   <si>
     <t>5000</t>
@@ -240,7 +240,7 @@
     <t>Bienes muebles e inmuebles</t>
   </si>
   <si>
-    <t>5786730</t>
+    <t>8093964</t>
   </si>
 </sst>
 </file>
@@ -639,13 +639,13 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="226.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="169.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="77.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -869,7 +869,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.85546875" bestFit="1" customWidth="1"/>
